--- a/Data/FlightPlan/FPL_29AUG26.xlsx
+++ b/Data/FlightPlan/FPL_29AUG26.xlsx
@@ -740,6 +740,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:34</t>
+  </si>
+  <si>
     <t>09:05</t>
   </si>
   <si>
@@ -1154,6 +1157,24 @@
     <t>VN-A670</t>
   </si>
   <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
     <t>VN-A671</t>
   </si>
   <si>
@@ -1202,24 +1223,6 @@
     <t>VN-A684</t>
   </si>
   <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
     <t>VN-A685</t>
   </si>
   <si>
@@ -1247,9 +1250,6 @@
     <t>VN-A811</t>
   </si>
   <si>
-    <t>OVB</t>
-  </si>
-  <si>
     <t>ALA</t>
   </si>
   <si>
@@ -1292,10 +1292,10 @@
     <t>VN-A820</t>
   </si>
   <si>
-    <t>Total Record(s): 449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated on  Aug 29, 2026 02:05</t>
+    <t>Total Record(s): 448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated on  Aug 29, 2026 04:32</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6612,7 +6612,9 @@
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
-      <c r="M164" s="7"/>
+      <c t="s" r="M164" s="7">
+        <v>243</v>
+      </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c t="s" r="A165" s="6">
@@ -6638,10 +6640,10 @@
         <v>147</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6674,7 +6676,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6773,7 +6775,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6806,7 +6808,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6818,7 +6820,7 @@
         <v>93</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>224</v>
@@ -6839,7 +6841,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6851,10 +6853,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6872,7 +6874,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6881,13 +6883,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>128</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6905,22 +6907,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6953,7 +6955,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6968,7 +6970,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6986,7 +6988,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6995,13 +6997,13 @@
         <v>227</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7019,13 +7021,13 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>227</v>
@@ -7052,7 +7054,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7064,10 +7066,10 @@
         <v>175</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7085,7 +7087,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7118,7 +7120,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7151,7 +7153,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7166,7 +7168,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7199,7 +7201,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7232,7 +7234,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7247,7 +7249,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="K185" s="7">
         <v>50</v>
@@ -7269,7 +7271,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7281,7 +7283,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>220</v>
@@ -7302,7 +7304,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7314,7 +7316,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>210</v>
@@ -7350,7 +7352,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7359,7 +7361,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>215</v>
@@ -7383,13 +7385,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>23</v>
@@ -7398,7 +7400,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7416,7 +7418,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7425,13 +7427,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7449,13 +7451,13 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>23</v>
@@ -7464,7 +7466,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7497,7 +7499,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7530,7 +7532,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7563,7 +7565,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7572,7 +7574,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>140</v>
@@ -7596,22 +7598,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7644,7 +7646,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7677,7 +7679,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7692,7 +7694,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7710,7 +7712,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7743,7 +7745,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7755,7 +7757,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>171</v>
@@ -7791,7 +7793,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7803,10 +7805,10 @@
         <v>227</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7824,7 +7826,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7839,7 +7841,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7857,7 +7859,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7869,10 +7871,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7890,7 +7892,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7923,7 +7925,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7935,7 +7937,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>34</v>
@@ -7956,7 +7958,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7989,7 +7991,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8001,7 +8003,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>150</v>
@@ -8022,7 +8024,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8037,7 +8039,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8070,7 +8072,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8103,7 +8105,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8136,7 +8138,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8169,7 +8171,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8202,7 +8204,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8235,7 +8237,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8250,7 +8252,7 @@
         <v>171</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8268,7 +8270,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8280,7 +8282,7 @@
         <v>122</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>27</v>
@@ -8316,7 +8318,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8349,7 +8351,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8361,7 +8363,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>177</v>
@@ -8382,7 +8384,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8394,10 +8396,10 @@
         <v>227</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8415,7 +8417,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8448,7 +8450,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8457,7 +8459,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I225" s="7">
         <v>110</v>
@@ -8481,13 +8483,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>23</v>
@@ -8514,7 +8516,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8526,7 +8528,7 @@
         <v>227</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>213</v>
@@ -8547,7 +8549,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8559,10 +8561,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8595,7 +8597,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8604,10 +8606,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>123</v>
@@ -8628,22 +8630,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8661,7 +8663,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8694,7 +8696,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8727,7 +8729,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8775,7 +8777,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8808,7 +8810,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8817,7 +8819,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>33</v>
@@ -8841,13 +8843,13 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>16</v>
@@ -8889,7 +8891,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8901,10 +8903,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8922,7 +8924,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8937,7 +8939,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8955,7 +8957,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8967,10 +8969,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8988,7 +8990,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9021,7 +9023,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9030,7 +9032,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>111</v>
@@ -9054,19 +9056,19 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>113</v>
@@ -9087,7 +9089,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9096,13 +9098,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I246" s="7">
         <v>173</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9120,22 +9122,22 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9168,7 +9170,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9177,13 +9179,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I249" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9201,13 +9203,13 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>23</v>
@@ -9234,7 +9236,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9246,7 +9248,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>67</v>
@@ -9267,7 +9269,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9300,7 +9302,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9333,7 +9335,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9381,7 +9383,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9393,7 +9395,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>60</v>
@@ -9414,7 +9416,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9423,13 +9425,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9447,13 +9449,13 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>16</v>
@@ -9480,7 +9482,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9489,10 +9491,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>139</v>
@@ -9513,13 +9515,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>16</v>
@@ -9546,7 +9548,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9561,7 +9563,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9594,7 +9596,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9606,10 +9608,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9627,7 +9629,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9660,7 +9662,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9708,7 +9710,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9741,7 +9743,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9756,7 +9758,7 @@
         <v>221</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9774,7 +9776,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9807,7 +9809,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9840,7 +9842,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9855,7 +9857,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9873,7 +9875,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9885,7 +9887,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>75</v>
@@ -9906,7 +9908,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9918,7 +9920,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>39</v>
@@ -9954,7 +9956,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9987,7 +9989,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9996,13 +9998,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>177</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10020,13 +10022,13 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>23</v>
@@ -10053,7 +10055,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10065,7 +10067,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>20</v>
@@ -10086,7 +10088,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10101,7 +10103,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10119,7 +10121,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10134,7 +10136,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10152,7 +10154,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10200,7 +10202,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10212,7 +10214,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>51</v>
@@ -10233,7 +10235,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10245,7 +10247,7 @@
         <v>227</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>88</v>
@@ -10266,7 +10268,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10310,26 +10312,26 @@
         <v>30</v>
       </c>
       <c t="s" r="C287" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10362,7 +10364,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10395,7 +10397,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10410,7 +10412,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10428,7 +10430,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10476,7 +10478,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10509,7 +10511,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10527,11 +10529,11 @@
         <v>166</v>
       </c>
       <c t="s" r="K294" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10546,7 +10548,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10583,7 +10585,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10616,7 +10618,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10631,7 +10633,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10649,7 +10651,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10658,13 +10660,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10682,22 +10684,22 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10730,7 +10732,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10742,7 +10744,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>120</v>
@@ -10763,7 +10765,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10772,10 +10774,10 @@
         <v>46</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>200</v>
@@ -10796,19 +10798,19 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>133</v>
@@ -10829,7 +10831,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10862,7 +10864,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10874,7 +10876,7 @@
         <v>103</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>224</v>
@@ -10895,7 +10897,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10907,10 +10909,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10928,7 +10930,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10940,10 +10942,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10961,7 +10963,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11009,7 +11011,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11021,7 +11023,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>201</v>
@@ -11042,7 +11044,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11075,7 +11077,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11108,7 +11110,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11123,7 +11125,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11141,7 +11143,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11174,7 +11176,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11189,7 +11191,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11222,7 +11224,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11255,7 +11257,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11288,7 +11290,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11300,10 +11302,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11321,7 +11323,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11354,7 +11356,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11387,7 +11389,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11402,7 +11404,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11435,13 +11437,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>23</v>
@@ -11450,7 +11452,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11468,7 +11470,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11477,7 +11479,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>117</v>
@@ -11516,7 +11518,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11531,7 +11533,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11549,7 +11551,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11561,7 +11563,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>107</v>
@@ -11582,7 +11584,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11615,7 +11617,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11624,7 +11626,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>224</v>
@@ -11648,13 +11650,13 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>23</v>
@@ -11689,14 +11691,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B333" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11711,14 +11713,14 @@
         <v>164</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="K333" s="7">
         <v>164</v>
       </c>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -11726,14 +11728,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B334" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11748,14 +11750,14 @@
         <v>29</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="K334" s="7">
         <v>29</v>
       </c>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -11763,14 +11765,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B335" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11807,7 +11809,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11816,13 +11818,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="I336" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11840,13 +11842,13 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>23</v>
@@ -11873,7 +11875,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11882,7 +11884,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>169</v>
@@ -11906,22 +11908,22 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11954,7 +11956,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11963,7 +11965,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>91</v>
@@ -11987,13 +11989,13 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>23</v>
@@ -12020,7 +12022,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12029,7 +12031,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>80</v>
@@ -12053,13 +12055,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>23</v>
@@ -12068,7 +12070,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12086,7 +12088,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12119,7 +12121,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12134,7 +12136,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12152,7 +12154,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12185,7 +12187,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12233,7 +12235,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12248,7 +12250,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12266,7 +12268,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12281,7 +12283,7 @@
         <v>210</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12299,7 +12301,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12308,7 +12310,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="I352" s="7">
         <v>32</v>
@@ -12332,13 +12334,13 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>16</v>
@@ -12347,7 +12349,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12365,7 +12367,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12374,13 +12376,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12398,22 +12400,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12446,7 +12448,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12455,7 +12457,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>163</v>
@@ -12463,9 +12465,13 @@
       <c t="s" r="J357" s="7">
         <v>106</v>
       </c>
-      <c r="K357" s="7"/>
+      <c t="s" r="K357" s="7">
+        <v>26</v>
+      </c>
       <c r="L357" s="7"/>
-      <c r="M357" s="7"/>
+      <c t="s" r="M357" s="7">
+        <v>298</v>
+      </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
       <c t="s" r="A358" s="6">
@@ -12479,19 +12485,19 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>166</v>
@@ -12512,7 +12518,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12545,7 +12551,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12557,10 +12563,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12578,7 +12584,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12587,7 +12593,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="I361" s="7">
         <v>70</v>
@@ -12611,13 +12617,13 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>23</v>
@@ -12626,7 +12632,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12644,7 +12650,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12659,7 +12665,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12677,7 +12683,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12689,10 +12695,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12725,7 +12731,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12758,7 +12764,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12791,7 +12797,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -12803,10 +12809,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12824,7 +12830,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12836,7 +12842,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>184</v>
@@ -12857,7 +12863,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -12869,10 +12875,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12890,7 +12896,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12902,7 +12908,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>40</v>
@@ -12938,7 +12944,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12947,10 +12953,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>105</v>
@@ -12971,13 +12977,13 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>16</v>
@@ -13004,7 +13010,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13037,7 +13043,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13052,7 +13058,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13070,7 +13076,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13103,7 +13109,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13136,7 +13142,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13169,7 +13175,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13181,7 +13187,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>89</v>
@@ -13217,7 +13223,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13250,7 +13256,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13259,7 +13265,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>165</v>
@@ -13283,19 +13289,19 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>124</v>
@@ -13316,7 +13322,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13328,10 +13334,10 @@
         <v>103</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13349,7 +13355,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13361,10 +13367,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13382,7 +13388,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13415,7 +13421,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13430,7 +13436,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13463,7 +13469,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13472,13 +13478,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13496,13 +13502,13 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>24</v>
@@ -13529,7 +13535,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13538,7 +13544,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>169</v>
@@ -13562,19 +13568,19 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>207</v>
@@ -13595,7 +13601,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13643,7 +13649,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13676,7 +13682,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13688,7 +13694,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>201</v>
@@ -13709,7 +13715,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13721,10 +13727,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13742,7 +13748,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13790,7 +13796,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -13799,7 +13805,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>41</v>
@@ -13823,13 +13829,13 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>23</v>
@@ -13838,7 +13844,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13856,7 +13862,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -13889,7 +13895,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -13922,7 +13928,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -13955,7 +13961,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -13970,7 +13976,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13988,7 +13994,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -14000,7 +14006,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>207</v>
@@ -14021,7 +14027,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -14036,7 +14042,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14062,14 +14068,14 @@
         <v>13</v>
       </c>
       <c r="B410" s="7">
-        <v>124</v>
+        <v>1362</v>
       </c>
       <c t="s" r="C410" s="7">
         <v>14</v>
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14078,13 +14084,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>297</v>
+        <v>164</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14095,29 +14101,29 @@
         <v>13</v>
       </c>
       <c r="B411" s="7">
-        <v>129</v>
+        <v>1363</v>
       </c>
       <c t="s" r="C411" s="7">
         <v>14</v>
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>256</v>
+        <v>28</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14128,14 +14134,14 @@
         <v>13</v>
       </c>
       <c r="B412" s="7">
-        <v>1612</v>
+        <v>272</v>
       </c>
       <c t="s" r="C412" s="7">
         <v>14</v>
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14144,13 +14150,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14161,29 +14167,29 @@
         <v>13</v>
       </c>
       <c r="B413" s="7">
-        <v>5530</v>
+        <v>7078</v>
       </c>
       <c t="s" r="C413" s="7">
         <v>14</v>
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>342</v>
+        <v>228</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>159</v>
+        <v>383</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14194,29 +14200,29 @@
         <v>13</v>
       </c>
       <c r="B414" s="7">
-        <v>5531</v>
+        <v>7079</v>
       </c>
       <c t="s" r="C414" s="7">
         <v>14</v>
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14227,55 +14233,73 @@
         <v>13</v>
       </c>
       <c r="B415" s="7">
-        <v>1613</v>
+        <v>273</v>
       </c>
       <c t="s" r="C415" s="7">
         <v>14</v>
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c r="M415" s="7"/>
     </row>
     <row r="416" ht="14.25" customHeight="1">
-      <c r="A416" s="6"/>
-      <c r="B416" s="7"/>
-      <c r="C416" s="7"/>
+      <c t="s" r="A416" s="6">
+        <v>13</v>
+      </c>
+      <c r="B416" s="7">
+        <v>3908</v>
+      </c>
+      <c t="s" r="C416" s="7">
+        <v>14</v>
+      </c>
       <c r="D416" s="7"/>
-      <c r="E416" s="7"/>
-      <c r="F416" s="7"/>
-      <c r="G416" s="8"/>
-      <c r="H416" s="8"/>
-      <c r="I416" s="7"/>
-      <c r="J416" s="7"/>
+      <c t="s" r="E416" s="7">
+        <v>381</v>
+      </c>
+      <c r="F416" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G416" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H416" s="8">
+        <v>304</v>
+      </c>
+      <c t="s" r="I416" s="7">
+        <v>384</v>
+      </c>
+      <c t="s" r="J416" s="7">
+        <v>385</v>
+      </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c r="M416" s="7"/>
     </row>
     <row r="417" ht="14.25" customHeight="1">
       <c t="s" r="A417" s="6">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="B417" s="7">
-        <v>212</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C417" s="7">
         <v>14</v>
@@ -14285,53 +14309,35 @@
         <v>381</v>
       </c>
       <c r="F417" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>23</v>
+        <v>304</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>18</v>
+        <v>386</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>239</v>
+        <v>387</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c r="M417" s="7"/>
     </row>
     <row r="418" ht="14.25" customHeight="1">
-      <c t="s" r="A418" s="6">
-        <v>13</v>
-      </c>
-      <c r="B418" s="7">
-        <v>215</v>
-      </c>
-      <c t="s" r="C418" s="7">
-        <v>14</v>
-      </c>
+      <c r="A418" s="6"/>
+      <c r="B418" s="7"/>
+      <c r="C418" s="7"/>
       <c r="D418" s="7"/>
-      <c t="s" r="E418" s="7">
-        <v>381</v>
-      </c>
-      <c r="F418" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G418" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="H418" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="I418" s="7">
-        <v>192</v>
-      </c>
-      <c t="s" r="J418" s="7">
-        <v>178</v>
-      </c>
+      <c r="E418" s="7"/>
+      <c r="F418" s="7"/>
+      <c r="G418" s="8"/>
+      <c r="H418" s="8"/>
+      <c r="I418" s="7"/>
+      <c r="J418" s="7"/>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c r="M418" s="7"/>
@@ -14341,14 +14347,14 @@
         <v>13</v>
       </c>
       <c r="B419" s="7">
-        <v>278</v>
+        <v>212</v>
       </c>
       <c t="s" r="C419" s="7">
         <v>14</v>
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -14357,13 +14363,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>227</v>
+        <v>46</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>342</v>
+        <v>18</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14374,29 +14380,29 @@
         <v>13</v>
       </c>
       <c r="B420" s="7">
-        <v>279</v>
+        <v>215</v>
       </c>
       <c t="s" r="C420" s="7">
         <v>14</v>
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>227</v>
+        <v>46</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>269</v>
+        <v>178</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14407,14 +14413,14 @@
         <v>13</v>
       </c>
       <c r="B421" s="7">
-        <v>1216</v>
+        <v>278</v>
       </c>
       <c t="s" r="C421" s="7">
         <v>14</v>
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14423,13 +14429,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>46</v>
+        <v>227</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>383</v>
+        <v>34</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14440,45 +14446,63 @@
         <v>13</v>
       </c>
       <c r="B422" s="7">
-        <v>1217</v>
+        <v>279</v>
       </c>
       <c t="s" r="C422" s="7">
         <v>14</v>
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>46</v>
+        <v>227</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c r="M422" s="7"/>
     </row>
     <row r="423" ht="14.25" customHeight="1">
-      <c r="A423" s="6"/>
-      <c r="B423" s="7"/>
-      <c r="C423" s="7"/>
+      <c t="s" r="A423" s="6">
+        <v>13</v>
+      </c>
+      <c r="B423" s="7">
+        <v>1216</v>
+      </c>
+      <c t="s" r="C423" s="7">
+        <v>14</v>
+      </c>
       <c r="D423" s="7"/>
-      <c r="E423" s="7"/>
-      <c r="F423" s="7"/>
-      <c r="G423" s="8"/>
-      <c r="H423" s="8"/>
-      <c r="I423" s="7"/>
-      <c r="J423" s="7"/>
+      <c t="s" r="E423" s="7">
+        <v>388</v>
+      </c>
+      <c r="F423" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G423" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H423" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="I423" s="7">
+        <v>389</v>
+      </c>
+      <c t="s" r="J423" s="7">
+        <v>390</v>
+      </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c r="M423" s="7"/>
@@ -14488,63 +14512,45 @@
         <v>13</v>
       </c>
       <c r="B424" s="7">
-        <v>1372</v>
+        <v>1217</v>
       </c>
       <c t="s" r="C424" s="7">
         <v>14</v>
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>348</v>
+        <v>23</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c r="M424" s="7"/>
     </row>
     <row r="425" ht="15" customHeight="1">
-      <c t="s" r="A425" s="6">
-        <v>13</v>
-      </c>
-      <c r="B425" s="7">
-        <v>1373</v>
-      </c>
-      <c t="s" r="C425" s="7">
-        <v>14</v>
-      </c>
+      <c r="A425" s="6"/>
+      <c r="B425" s="7"/>
+      <c r="C425" s="7"/>
       <c r="D425" s="7"/>
-      <c t="s" r="E425" s="7">
-        <v>384</v>
-      </c>
-      <c r="F425" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G425" s="8">
-        <v>348</v>
-      </c>
-      <c t="s" r="H425" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="I425" s="7">
-        <v>27</v>
-      </c>
-      <c t="s" r="J425" s="7">
-        <v>28</v>
-      </c>
+      <c r="E425" s="7"/>
+      <c r="F425" s="7"/>
+      <c r="G425" s="8"/>
+      <c r="H425" s="8"/>
+      <c r="I425" s="7"/>
+      <c r="J425" s="7"/>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c r="M425" s="7"/>
@@ -14554,14 +14560,14 @@
         <v>13</v>
       </c>
       <c r="B426" s="7">
-        <v>372</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C426" s="7">
         <v>14</v>
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -14570,13 +14576,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14587,29 +14593,29 @@
         <v>13</v>
       </c>
       <c r="B427" s="7">
-        <v>373</v>
+        <v>1373</v>
       </c>
       <c t="s" r="C427" s="7">
         <v>14</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14620,14 +14626,14 @@
         <v>13</v>
       </c>
       <c r="B428" s="7">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c t="s" r="C428" s="7">
         <v>14</v>
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14636,13 +14642,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>16</v>
+        <v>349</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>276</v>
+        <v>47</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14653,29 +14659,29 @@
         <v>13</v>
       </c>
       <c r="B429" s="7">
-        <v>151</v>
+        <v>373</v>
       </c>
       <c t="s" r="C429" s="7">
         <v>14</v>
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>16</v>
+        <v>349</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14686,14 +14692,14 @@
         <v>13</v>
       </c>
       <c r="B430" s="7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c t="s" r="C430" s="7">
         <v>14</v>
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -14705,10 +14711,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>382</v>
+        <v>277</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14716,17 +14722,17 @@
     </row>
     <row r="431" ht="14.25" customHeight="1">
       <c t="s" r="A431" s="6">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="B431" s="7">
-        <v>1980</v>
+        <v>151</v>
       </c>
       <c t="s" r="C431" s="7">
         <v>14</v>
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -14735,95 +14741,95 @@
         <v>16</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>385</v>
+        <v>23</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c r="M431" s="7"/>
     </row>
     <row r="432" ht="14.25" customHeight="1">
-      <c r="A432" s="6"/>
-      <c r="B432" s="7"/>
-      <c r="C432" s="7"/>
+      <c t="s" r="A432" s="6">
+        <v>13</v>
+      </c>
+      <c r="B432" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="C432" s="7">
+        <v>14</v>
+      </c>
       <c r="D432" s="7"/>
-      <c r="E432" s="7"/>
-      <c r="F432" s="7"/>
-      <c r="G432" s="8"/>
-      <c r="H432" s="8"/>
-      <c r="I432" s="7"/>
-      <c r="J432" s="7"/>
+      <c t="s" r="E432" s="7">
+        <v>391</v>
+      </c>
+      <c r="F432" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G432" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H432" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I432" s="7">
+        <v>389</v>
+      </c>
+      <c t="s" r="J432" s="7">
+        <v>173</v>
+      </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c r="M432" s="7"/>
     </row>
     <row r="433" ht="14.25" customHeight="1">
       <c t="s" r="A433" s="6">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="B433" s="7">
-        <v>581</v>
+        <v>1980</v>
       </c>
       <c t="s" r="C433" s="7">
         <v>14</v>
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F433" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>97</v>
+        <v>392</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>316</v>
+        <v>119</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c r="M433" s="7"/>
     </row>
     <row r="434" ht="14.25" customHeight="1">
-      <c t="s" r="A434" s="6">
-        <v>13</v>
-      </c>
-      <c r="B434" s="7">
-        <v>582</v>
-      </c>
-      <c t="s" r="C434" s="7">
-        <v>14</v>
-      </c>
+      <c r="A434" s="6"/>
+      <c r="B434" s="7"/>
+      <c r="C434" s="7"/>
       <c r="D434" s="7"/>
-      <c t="s" r="E434" s="7">
-        <v>386</v>
-      </c>
-      <c r="F434" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G434" s="8">
-        <v>97</v>
-      </c>
-      <c t="s" r="H434" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I434" s="7">
-        <v>18</v>
-      </c>
-      <c t="s" r="J434" s="7">
-        <v>29</v>
-      </c>
+      <c r="E434" s="7"/>
+      <c r="F434" s="7"/>
+      <c r="G434" s="8"/>
+      <c r="H434" s="8"/>
+      <c r="I434" s="7"/>
+      <c r="J434" s="7"/>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c r="M434" s="7"/>
@@ -14833,14 +14839,14 @@
         <v>13</v>
       </c>
       <c r="B435" s="7">
-        <v>720</v>
+        <v>581</v>
       </c>
       <c t="s" r="C435" s="7">
         <v>14</v>
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -14849,13 +14855,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>177</v>
+        <v>317</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14866,29 +14872,29 @@
         <v>13</v>
       </c>
       <c r="B436" s="7">
-        <v>721</v>
+        <v>582</v>
       </c>
       <c t="s" r="C436" s="7">
         <v>14</v>
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>235</v>
+        <v>18</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>257</v>
+        <v>29</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14899,14 +14905,14 @@
         <v>13</v>
       </c>
       <c r="B437" s="7">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c t="s" r="C437" s="7">
         <v>14</v>
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -14915,13 +14921,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>62</v>
+        <v>177</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>267</v>
+        <v>201</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14932,29 +14938,29 @@
         <v>13</v>
       </c>
       <c r="B438" s="7">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c t="s" r="C438" s="7">
         <v>14</v>
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>110</v>
+        <v>235</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14965,14 +14971,14 @@
         <v>13</v>
       </c>
       <c r="B439" s="7">
-        <v>722</v>
+        <v>703</v>
       </c>
       <c t="s" r="C439" s="7">
         <v>14</v>
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14981,13 +14987,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>259</v>
+        <v>62</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14998,45 +15004,63 @@
         <v>13</v>
       </c>
       <c r="B440" s="7">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c t="s" r="C440" s="7">
         <v>14</v>
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c r="M440" s="7"/>
     </row>
     <row r="441" ht="14.25" customHeight="1">
-      <c r="A441" s="6"/>
-      <c r="B441" s="7"/>
-      <c r="C441" s="7"/>
+      <c t="s" r="A441" s="6">
+        <v>13</v>
+      </c>
+      <c r="B441" s="7">
+        <v>722</v>
+      </c>
+      <c t="s" r="C441" s="7">
+        <v>14</v>
+      </c>
       <c r="D441" s="7"/>
-      <c r="E441" s="7"/>
-      <c r="F441" s="7"/>
-      <c r="G441" s="8"/>
-      <c r="H441" s="8"/>
-      <c r="I441" s="7"/>
-      <c r="J441" s="7"/>
+      <c t="s" r="E441" s="7">
+        <v>393</v>
+      </c>
+      <c r="F441" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G441" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H441" s="8">
+        <v>227</v>
+      </c>
+      <c t="s" r="I441" s="7">
+        <v>260</v>
+      </c>
+      <c t="s" r="J441" s="7">
+        <v>295</v>
+      </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c r="M441" s="7"/>
@@ -15046,63 +15070,45 @@
         <v>13</v>
       </c>
       <c r="B442" s="7">
-        <v>801</v>
+        <v>723</v>
       </c>
       <c t="s" r="C442" s="7">
         <v>14</v>
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F442" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>23</v>
+        <v>227</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>347</v>
+        <v>88</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>352</v>
+        <v>195</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c r="M442" s="7"/>
     </row>
     <row r="443" ht="14.25" customHeight="1">
-      <c t="s" r="A443" s="6">
-        <v>13</v>
-      </c>
-      <c r="B443" s="7">
-        <v>802</v>
-      </c>
-      <c t="s" r="C443" s="7">
-        <v>14</v>
-      </c>
+      <c r="A443" s="6"/>
+      <c r="B443" s="7"/>
+      <c r="C443" s="7"/>
       <c r="D443" s="7"/>
-      <c t="s" r="E443" s="7">
-        <v>387</v>
-      </c>
-      <c r="F443" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G443" s="8">
-        <v>63</v>
-      </c>
-      <c t="s" r="H443" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="I443" s="7">
-        <v>49</v>
-      </c>
-      <c t="s" r="J443" s="7">
-        <v>135</v>
-      </c>
+      <c r="E443" s="7"/>
+      <c r="F443" s="7"/>
+      <c r="G443" s="8"/>
+      <c r="H443" s="8"/>
+      <c r="I443" s="7"/>
+      <c r="J443" s="7"/>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c r="M443" s="7"/>
@@ -15112,14 +15118,14 @@
         <v>13</v>
       </c>
       <c r="B444" s="7">
-        <v>362</v>
+        <v>801</v>
       </c>
       <c t="s" r="C444" s="7">
         <v>14</v>
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
@@ -15128,13 +15134,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>33</v>
+        <v>348</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>19</v>
+        <v>353</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15145,29 +15151,29 @@
         <v>13</v>
       </c>
       <c r="B445" s="7">
-        <v>363</v>
+        <v>802</v>
       </c>
       <c t="s" r="C445" s="7">
         <v>14</v>
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>180</v>
+        <v>49</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15178,14 +15184,14 @@
         <v>13</v>
       </c>
       <c r="B446" s="7">
-        <v>3948</v>
+        <v>362</v>
       </c>
       <c t="s" r="C446" s="7">
         <v>14</v>
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15194,13 +15200,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>388</v>
+        <v>43</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>232</v>
+        <v>19</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15208,114 +15214,114 @@
     </row>
     <row r="447" ht="14.25" customHeight="1">
       <c t="s" r="A447" s="6">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="B447" s="7">
-        <v>3949</v>
+        <v>363</v>
       </c>
       <c t="s" r="C447" s="7">
         <v>14</v>
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>388</v>
+        <v>43</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>288</v>
+        <v>180</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>334</v>
+        <v>139</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c r="M447" s="7"/>
     </row>
     <row r="448" ht="14.25" customHeight="1">
-      <c r="A448" s="6"/>
-      <c r="B448" s="7"/>
-      <c r="C448" s="7"/>
+      <c t="s" r="A448" s="6">
+        <v>13</v>
+      </c>
+      <c r="B448" s="7">
+        <v>3948</v>
+      </c>
+      <c t="s" r="C448" s="7">
+        <v>14</v>
+      </c>
       <c r="D448" s="7"/>
-      <c r="E448" s="7"/>
-      <c r="F448" s="7"/>
-      <c r="G448" s="8"/>
-      <c r="H448" s="8"/>
-      <c r="I448" s="7"/>
-      <c r="J448" s="7"/>
+      <c t="s" r="E448" s="7">
+        <v>394</v>
+      </c>
+      <c r="F448" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G448" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H448" s="8">
+        <v>395</v>
+      </c>
+      <c t="s" r="I448" s="7">
+        <v>71</v>
+      </c>
+      <c t="s" r="J448" s="7">
+        <v>232</v>
+      </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c r="M448" s="7"/>
     </row>
     <row r="449" ht="14.25" customHeight="1">
       <c t="s" r="A449" s="6">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="B449" s="7">
-        <v>7638</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C449" s="7">
         <v>14</v>
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>16</v>
+        <v>395</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>390</v>
+        <v>23</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>178</v>
+        <v>289</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>180</v>
+        <v>335</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c r="M449" s="7"/>
     </row>
     <row r="450" ht="15" customHeight="1">
-      <c t="s" r="A450" s="6">
-        <v>13</v>
-      </c>
-      <c r="B450" s="7">
-        <v>7639</v>
-      </c>
-      <c t="s" r="C450" s="7">
-        <v>14</v>
-      </c>
+      <c r="A450" s="6"/>
+      <c r="B450" s="7"/>
+      <c r="C450" s="7"/>
       <c r="D450" s="7"/>
-      <c t="s" r="E450" s="7">
-        <v>389</v>
-      </c>
-      <c r="F450" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G450" s="8">
-        <v>390</v>
-      </c>
-      <c t="s" r="H450" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I450" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="J450" s="7">
-        <v>73</v>
-      </c>
+      <c r="E450" s="7"/>
+      <c r="F450" s="7"/>
+      <c r="G450" s="8"/>
+      <c r="H450" s="8"/>
+      <c r="I450" s="7"/>
+      <c r="J450" s="7"/>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c r="M450" s="7"/>
@@ -15325,14 +15331,14 @@
         <v>13</v>
       </c>
       <c r="B451" s="7">
-        <v>7712</v>
+        <v>7638</v>
       </c>
       <c t="s" r="C451" s="7">
         <v>14</v>
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -15341,13 +15347,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>391</v>
+        <v>180</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15355,129 +15361,147 @@
     </row>
     <row r="452" ht="14.25" customHeight="1">
       <c t="s" r="A452" s="6">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="B452" s="7">
-        <v>7713</v>
+        <v>7639</v>
       </c>
       <c t="s" r="C452" s="7">
         <v>14</v>
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>392</v>
+        <v>73</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c r="M452" s="7"/>
     </row>
     <row r="453" ht="14.25" customHeight="1">
-      <c r="A453" s="6"/>
-      <c r="B453" s="7"/>
-      <c r="C453" s="7"/>
+      <c t="s" r="A453" s="6">
+        <v>13</v>
+      </c>
+      <c r="B453" s="7">
+        <v>7712</v>
+      </c>
+      <c t="s" r="C453" s="7">
+        <v>14</v>
+      </c>
       <c r="D453" s="7"/>
-      <c r="E453" s="7"/>
-      <c r="F453" s="7"/>
-      <c r="G453" s="8"/>
-      <c r="H453" s="8"/>
-      <c r="I453" s="7"/>
-      <c r="J453" s="7"/>
+      <c t="s" r="E453" s="7">
+        <v>396</v>
+      </c>
+      <c r="F453" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G453" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H453" s="8">
+        <v>395</v>
+      </c>
+      <c t="s" r="I453" s="7">
+        <v>205</v>
+      </c>
+      <c t="s" r="J453" s="7">
+        <v>398</v>
+      </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c r="M453" s="7"/>
     </row>
     <row r="454" ht="14.25" customHeight="1">
       <c t="s" r="A454" s="6">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="B454" s="7">
-        <v>28</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C454" s="7">
-        <v>323</v>
+        <v>14</v>
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F454" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>320</v>
+        <v>395</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>51</v>
+        <v>229</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>66</v>
+        <v>399</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c r="M454" s="7"/>
     </row>
     <row r="455" ht="15" customHeight="1">
-      <c t="s" r="A455" s="6">
-        <v>13</v>
-      </c>
-      <c r="B455" s="7">
-        <v>148</v>
-      </c>
-      <c t="s" r="C455" s="7">
-        <v>14</v>
-      </c>
+      <c r="A455" s="6"/>
+      <c r="B455" s="7"/>
+      <c r="C455" s="7"/>
       <c r="D455" s="7"/>
-      <c t="s" r="E455" s="7">
-        <v>393</v>
-      </c>
-      <c r="F455" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G455" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="H455" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I455" s="7">
-        <v>328</v>
-      </c>
-      <c t="s" r="J455" s="7">
-        <v>269</v>
-      </c>
+      <c r="E455" s="7"/>
+      <c r="F455" s="7"/>
+      <c r="G455" s="8"/>
+      <c r="H455" s="8"/>
+      <c r="I455" s="7"/>
+      <c r="J455" s="7"/>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c r="M455" s="7"/>
     </row>
     <row r="456" ht="14.25" customHeight="1">
-      <c r="A456" s="6"/>
-      <c r="B456" s="7"/>
-      <c r="C456" s="7"/>
+      <c t="s" r="A456" s="6">
+        <v>13</v>
+      </c>
+      <c r="B456" s="7">
+        <v>28</v>
+      </c>
+      <c t="s" r="C456" s="7">
+        <v>324</v>
+      </c>
       <c r="D456" s="7"/>
-      <c r="E456" s="7"/>
-      <c r="F456" s="7"/>
-      <c r="G456" s="8"/>
-      <c r="H456" s="8"/>
-      <c r="I456" s="7"/>
-      <c r="J456" s="7"/>
+      <c t="s" r="E456" s="7">
+        <v>400</v>
+      </c>
+      <c r="F456" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G456" s="8">
+        <v>321</v>
+      </c>
+      <c t="s" r="H456" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="I456" s="7">
+        <v>51</v>
+      </c>
+      <c t="s" r="J456" s="7">
+        <v>66</v>
+      </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
       <c r="M456" s="7"/>
@@ -15487,14 +15511,14 @@
         <v>13</v>
       </c>
       <c r="B457" s="7">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c t="s" r="C457" s="7">
         <v>14</v>
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -15506,44 +15530,26 @@
         <v>16</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
       <c r="M457" s="7"/>
     </row>
     <row r="458" ht="14.25" customHeight="1">
-      <c t="s" r="A458" s="6">
-        <v>13</v>
-      </c>
-      <c r="B458" s="7">
-        <v>131</v>
-      </c>
-      <c t="s" r="C458" s="7">
-        <v>14</v>
-      </c>
+      <c r="A458" s="6"/>
+      <c r="B458" s="7"/>
+      <c r="C458" s="7"/>
       <c r="D458" s="7"/>
-      <c t="s" r="E458" s="7">
-        <v>394</v>
-      </c>
-      <c r="F458" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G458" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H458" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="I458" s="7">
-        <v>30</v>
-      </c>
-      <c t="s" r="J458" s="7">
-        <v>96</v>
-      </c>
+      <c r="E458" s="7"/>
+      <c r="F458" s="7"/>
+      <c r="G458" s="8"/>
+      <c r="H458" s="8"/>
+      <c r="I458" s="7"/>
+      <c r="J458" s="7"/>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c r="M458" s="7"/>
@@ -15553,14 +15559,14 @@
         <v>13</v>
       </c>
       <c r="B459" s="7">
-        <v>636</v>
+        <v>126</v>
       </c>
       <c t="s" r="C459" s="7">
         <v>14</v>
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
@@ -15569,13 +15575,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>66</v>
+        <v>210</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15586,29 +15592,29 @@
         <v>13</v>
       </c>
       <c r="B460" s="7">
-        <v>633</v>
+        <v>131</v>
       </c>
       <c t="s" r="C460" s="7">
         <v>14</v>
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>267</v>
+        <v>30</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15619,14 +15625,14 @@
         <v>13</v>
       </c>
       <c r="B461" s="7">
-        <v>352</v>
+        <v>636</v>
       </c>
       <c t="s" r="C461" s="7">
         <v>14</v>
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F461" s="7">
         <v>321</v>
@@ -15635,13 +15641,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>294</v>
+        <v>135</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>186</v>
+        <v>66</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15652,29 +15658,29 @@
         <v>13</v>
       </c>
       <c r="B462" s="7">
-        <v>353</v>
+        <v>633</v>
       </c>
       <c t="s" r="C462" s="7">
         <v>14</v>
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F462" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c t="s" r="H462" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
@@ -15685,14 +15691,14 @@
         <v>13</v>
       </c>
       <c r="B463" s="7">
-        <v>652</v>
+        <v>352</v>
       </c>
       <c t="s" r="C463" s="7">
         <v>14</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -15701,13 +15707,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15718,45 +15724,63 @@
         <v>13</v>
       </c>
       <c r="B464" s="7">
-        <v>631</v>
+        <v>353</v>
       </c>
       <c t="s" r="C464" s="7">
         <v>14</v>
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>395</v>
+        <v>182</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c r="M464" s="7"/>
     </row>
     <row r="465" ht="15" customHeight="1">
-      <c r="A465" s="6"/>
-      <c r="B465" s="7"/>
-      <c r="C465" s="7"/>
+      <c t="s" r="A465" s="6">
+        <v>13</v>
+      </c>
+      <c r="B465" s="7">
+        <v>652</v>
+      </c>
+      <c t="s" r="C465" s="7">
+        <v>14</v>
+      </c>
       <c r="D465" s="7"/>
-      <c r="E465" s="7"/>
-      <c r="F465" s="7"/>
-      <c r="G465" s="8"/>
-      <c r="H465" s="8"/>
-      <c r="I465" s="7"/>
-      <c r="J465" s="7"/>
+      <c t="s" r="E465" s="7">
+        <v>401</v>
+      </c>
+      <c r="F465" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G465" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H465" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I465" s="7">
+        <v>344</v>
+      </c>
+      <c t="s" r="J465" s="7">
+        <v>130</v>
+      </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c r="M465" s="7"/>
@@ -15766,63 +15790,45 @@
         <v>13</v>
       </c>
       <c r="B466" s="7">
-        <v>1362</v>
+        <v>631</v>
       </c>
       <c t="s" r="C466" s="7">
         <v>14</v>
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>164</v>
+        <v>289</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
       <c r="M466" s="7"/>
     </row>
     <row r="467" ht="14.25" customHeight="1">
-      <c t="s" r="A467" s="6">
-        <v>13</v>
-      </c>
-      <c r="B467" s="7">
-        <v>1363</v>
-      </c>
-      <c t="s" r="C467" s="7">
-        <v>14</v>
-      </c>
+      <c r="A467" s="6"/>
+      <c r="B467" s="7"/>
+      <c r="C467" s="7"/>
       <c r="D467" s="7"/>
-      <c t="s" r="E467" s="7">
-        <v>396</v>
-      </c>
-      <c r="F467" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G467" s="8">
-        <v>43</v>
-      </c>
-      <c t="s" r="H467" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="I467" s="7">
-        <v>242</v>
-      </c>
-      <c t="s" r="J467" s="7">
-        <v>28</v>
-      </c>
+      <c r="E467" s="7"/>
+      <c r="F467" s="7"/>
+      <c r="G467" s="8"/>
+      <c r="H467" s="8"/>
+      <c r="I467" s="7"/>
+      <c r="J467" s="7"/>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
       <c r="M467" s="7"/>
@@ -15832,14 +15838,14 @@
         <v>13</v>
       </c>
       <c r="B468" s="7">
-        <v>272</v>
+        <v>124</v>
       </c>
       <c t="s" r="C468" s="7">
         <v>14</v>
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -15848,13 +15854,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H468" s="8">
-        <v>227</v>
+        <v>16</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>29</v>
+        <v>372</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>48</v>
+        <v>298</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
@@ -15865,29 +15871,29 @@
         <v>13</v>
       </c>
       <c r="B469" s="7">
-        <v>7078</v>
+        <v>129</v>
       </c>
       <c t="s" r="C469" s="7">
         <v>14</v>
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>227</v>
+        <v>16</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>376</v>
+        <v>23</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>398</v>
+        <v>257</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -15898,29 +15904,29 @@
         <v>13</v>
       </c>
       <c r="B470" s="7">
-        <v>7079</v>
+        <v>1612</v>
       </c>
       <c t="s" r="C470" s="7">
         <v>14</v>
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>376</v>
+        <v>23</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15931,29 +15937,29 @@
         <v>13</v>
       </c>
       <c r="B471" s="7">
-        <v>273</v>
+        <v>5530</v>
       </c>
       <c t="s" r="C471" s="7">
         <v>14</v>
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F471" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c t="s" r="H471" s="8">
-        <v>23</v>
+        <v>377</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -15964,29 +15970,29 @@
         <v>13</v>
       </c>
       <c r="B472" s="7">
-        <v>3908</v>
+        <v>5531</v>
       </c>
       <c t="s" r="C472" s="7">
         <v>14</v>
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F472" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G472" s="8">
-        <v>23</v>
+        <v>377</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>303</v>
+        <v>97</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>399</v>
+        <v>36</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>400</v>
+        <v>149</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -15994,32 +16000,32 @@
     </row>
     <row r="473" ht="14.25" customHeight="1">
       <c t="s" r="A473" s="6">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="B473" s="7">
-        <v>3909</v>
+        <v>1613</v>
       </c>
       <c t="s" r="C473" s="7">
         <v>14</v>
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F473" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>303</v>
+        <v>97</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>401</v>
+        <v>128</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>402</v>
+        <v>129</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16052,22 +16058,22 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F475" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G475" s="8">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c t="s" r="H475" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -16085,7 +16091,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F476" s="7">
         <v>321</v>
@@ -16094,7 +16100,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H476" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="I476" s="7">
         <v>62</v>
@@ -16118,13 +16124,13 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F477" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G477" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="H477" s="8">
         <v>16</v>
@@ -16151,7 +16157,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -16166,7 +16172,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J478" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
@@ -16184,7 +16190,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F479" s="7">
         <v>321</v>
@@ -16196,10 +16202,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
@@ -16232,7 +16238,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F481" s="7">
         <v>321</v>
@@ -16265,7 +16271,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F482" s="7">
         <v>321</v>
@@ -16277,7 +16283,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J482" s="7">
         <v>38</v>
@@ -16313,7 +16319,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F484" s="7">
         <v>320</v>
@@ -16325,7 +16331,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J484" s="7">
         <v>189</v>
@@ -16346,7 +16352,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F485" s="7">
         <v>320</v>
@@ -16358,7 +16364,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I485" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J485" s="7">
         <v>30</v>
@@ -16379,7 +16385,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F486" s="7">
         <v>320</v>
@@ -16412,7 +16418,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F487" s="7">
         <v>320</v>
@@ -16445,7 +16451,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F488" s="7">
         <v>320</v>
@@ -16478,7 +16484,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F489" s="7">
         <v>320</v>
@@ -16526,7 +16532,7 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F491" s="7">
         <v>321</v>
@@ -16559,7 +16565,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F492" s="7">
         <v>321</v>
@@ -16592,7 +16598,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F493" s="7">
         <v>321</v>
@@ -16625,7 +16631,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F494" s="7">
         <v>321</v>
@@ -16673,7 +16679,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F496" s="7">
         <v>321</v>
@@ -16685,7 +16691,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I496" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J496" s="7">
         <v>135</v>
@@ -16706,7 +16712,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F497" s="7">
         <v>321</v>
@@ -16739,7 +16745,7 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F498" s="7">
         <v>321</v>
@@ -16772,7 +16778,7 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F499" s="7">
         <v>321</v>
@@ -16784,7 +16790,7 @@
         <v>219</v>
       </c>
       <c t="s" r="I499" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J499" s="7">
         <v>28</v>
@@ -16820,7 +16826,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F501" s="7">
         <v>321</v>
@@ -16853,7 +16859,7 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F502" s="7">
         <v>321</v>
@@ -16886,7 +16892,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F503" s="7">
         <v>321</v>
@@ -16898,7 +16904,7 @@
         <v>93</v>
       </c>
       <c t="s" r="I503" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J503" s="7">
         <v>193</v>
@@ -16919,7 +16925,7 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F504" s="7">
         <v>321</v>
@@ -16952,7 +16958,7 @@
       </c>
       <c r="D505" s="7"/>
       <c t="s" r="E505" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F505" s="7">
         <v>321</v>
@@ -16967,7 +16973,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J505" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K505" s="7"/>
       <c r="L505" s="7"/>
@@ -16985,7 +16991,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F506" s="7">
         <v>321</v>
@@ -17018,7 +17024,7 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F507" s="7">
         <v>321</v>
@@ -17027,7 +17033,7 @@
         <v>23</v>
       </c>
       <c t="s" r="H507" s="8">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="I507" s="7">
         <v>160</v>
@@ -17051,13 +17057,13 @@
       </c>
       <c r="D508" s="7"/>
       <c t="s" r="E508" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F508" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G508" s="8">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="H508" s="8">
         <v>23</v>
@@ -17066,7 +17072,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J508" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K508" s="7"/>
       <c r="L508" s="7"/>
@@ -17099,7 +17105,7 @@
       </c>
       <c r="D510" s="7"/>
       <c t="s" r="E510" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F510" s="7">
         <v>320</v>
@@ -17114,7 +17120,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J510" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
@@ -17132,7 +17138,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F511" s="7">
         <v>320</v>
@@ -17144,7 +17150,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I511" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J511" s="7">
         <v>110</v>
@@ -17165,7 +17171,7 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F512" s="7">
         <v>320</v>
@@ -17198,7 +17204,7 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F513" s="7">
         <v>320</v>
@@ -17227,11 +17233,11 @@
         <v>716</v>
       </c>
       <c t="s" r="C514" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D514" s="7"/>
       <c t="s" r="E514" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F514" s="7">
         <v>320</v>
@@ -17246,7 +17252,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J514" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K514" s="7"/>
       <c r="L514" s="7"/>
@@ -17272,29 +17278,29 @@
         <v>13</v>
       </c>
       <c r="B516" s="7">
-        <v>5061</v>
+        <v>1580</v>
       </c>
       <c t="s" r="C516" s="7">
         <v>14</v>
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F516" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G516" s="8">
-        <v>412</v>
+        <v>97</v>
       </c>
       <c t="s" r="H516" s="8">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c t="s" r="I516" s="7">
-        <v>392</v>
+        <v>64</v>
       </c>
       <c t="s" r="J516" s="7">
-        <v>283</v>
+        <v>148</v>
       </c>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
@@ -17305,29 +17311,29 @@
         <v>13</v>
       </c>
       <c r="B517" s="7">
-        <v>1580</v>
+        <v>51</v>
       </c>
       <c t="s" r="C517" s="7">
         <v>14</v>
       </c>
       <c r="D517" s="7"/>
       <c t="s" r="E517" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F517" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G517" s="8">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c t="s" r="H517" s="8">
-        <v>24</v>
+        <v>413</v>
       </c>
       <c t="s" r="I517" s="7">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c t="s" r="J517" s="7">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
@@ -17338,78 +17344,78 @@
         <v>13</v>
       </c>
       <c r="B518" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="C518" s="7">
         <v>14</v>
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F518" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G518" s="8">
+        <v>413</v>
+      </c>
+      <c t="s" r="H518" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H518" s="8">
-        <v>413</v>
-      </c>
       <c t="s" r="I518" s="7">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c t="s" r="J518" s="7">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="K518" s="7"/>
       <c r="L518" s="7"/>
       <c r="M518" s="7"/>
     </row>
     <row r="519" ht="14.25" customHeight="1">
-      <c t="s" r="A519" s="6">
-        <v>13</v>
-      </c>
-      <c r="B519" s="7">
-        <v>52</v>
-      </c>
-      <c t="s" r="C519" s="7">
-        <v>14</v>
-      </c>
+      <c r="A519" s="6"/>
+      <c r="B519" s="7"/>
+      <c r="C519" s="7"/>
       <c r="D519" s="7"/>
-      <c t="s" r="E519" s="7">
-        <v>411</v>
-      </c>
-      <c r="F519" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G519" s="8">
-        <v>413</v>
-      </c>
-      <c t="s" r="H519" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I519" s="7">
-        <v>39</v>
-      </c>
-      <c t="s" r="J519" s="7">
-        <v>154</v>
-      </c>
+      <c r="E519" s="7"/>
+      <c r="F519" s="7"/>
+      <c r="G519" s="8"/>
+      <c r="H519" s="8"/>
+      <c r="I519" s="7"/>
+      <c r="J519" s="7"/>
       <c r="K519" s="7"/>
       <c r="L519" s="7"/>
       <c r="M519" s="7"/>
     </row>
     <row r="520" ht="15" customHeight="1">
-      <c r="A520" s="6"/>
-      <c r="B520" s="7"/>
-      <c r="C520" s="7"/>
+      <c t="s" r="A520" s="6">
+        <v>13</v>
+      </c>
+      <c r="B520" s="7">
+        <v>8931</v>
+      </c>
+      <c t="s" r="C520" s="7">
+        <v>14</v>
+      </c>
       <c r="D520" s="7"/>
-      <c r="E520" s="7"/>
-      <c r="F520" s="7"/>
-      <c r="G520" s="8"/>
-      <c r="H520" s="8"/>
-      <c r="I520" s="7"/>
-      <c r="J520" s="7"/>
+      <c t="s" r="E520" s="7">
+        <v>414</v>
+      </c>
+      <c r="F520" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G520" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H520" s="8">
+        <v>415</v>
+      </c>
+      <c t="s" r="I520" s="7">
+        <v>27</v>
+      </c>
+      <c t="s" r="J520" s="7">
+        <v>109</v>
+      </c>
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
       <c r="M520" s="7"/>
@@ -17419,7 +17425,7 @@
         <v>13</v>
       </c>
       <c r="B521" s="7">
-        <v>8931</v>
+        <v>8932</v>
       </c>
       <c t="s" r="C521" s="7">
         <v>14</v>
@@ -17432,65 +17438,65 @@
         <v>330</v>
       </c>
       <c t="s" r="G521" s="8">
+        <v>415</v>
+      </c>
+      <c t="s" r="H521" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H521" s="8">
-        <v>415</v>
-      </c>
       <c t="s" r="I521" s="7">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c t="s" r="J521" s="7">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="K521" s="7"/>
       <c r="L521" s="7"/>
       <c r="M521" s="7"/>
     </row>
     <row r="522" ht="14.25" customHeight="1">
-      <c t="s" r="A522" s="6">
-        <v>13</v>
-      </c>
-      <c r="B522" s="7">
-        <v>8932</v>
-      </c>
-      <c t="s" r="C522" s="7">
-        <v>14</v>
-      </c>
+      <c r="A522" s="6"/>
+      <c r="B522" s="7"/>
+      <c r="C522" s="7"/>
       <c r="D522" s="7"/>
-      <c t="s" r="E522" s="7">
-        <v>414</v>
-      </c>
-      <c r="F522" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G522" s="8">
-        <v>415</v>
-      </c>
-      <c t="s" r="H522" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I522" s="7">
-        <v>110</v>
-      </c>
-      <c t="s" r="J522" s="7">
-        <v>152</v>
-      </c>
+      <c r="E522" s="7"/>
+      <c r="F522" s="7"/>
+      <c r="G522" s="8"/>
+      <c r="H522" s="8"/>
+      <c r="I522" s="7"/>
+      <c r="J522" s="7"/>
       <c r="K522" s="7"/>
       <c r="L522" s="7"/>
       <c r="M522" s="7"/>
     </row>
     <row r="523" ht="14.25" customHeight="1">
-      <c r="A523" s="6"/>
-      <c r="B523" s="7"/>
-      <c r="C523" s="7"/>
+      <c t="s" r="A523" s="6">
+        <v>13</v>
+      </c>
+      <c r="B523" s="7">
+        <v>2831</v>
+      </c>
+      <c t="s" r="C523" s="7">
+        <v>136</v>
+      </c>
       <c r="D523" s="7"/>
-      <c r="E523" s="7"/>
-      <c r="F523" s="7"/>
-      <c r="G523" s="8"/>
-      <c r="H523" s="8"/>
-      <c r="I523" s="7"/>
-      <c r="J523" s="7"/>
+      <c t="s" r="E523" s="7">
+        <v>416</v>
+      </c>
+      <c r="F523" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G523" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H523" s="8">
+        <v>417</v>
+      </c>
+      <c t="s" r="I523" s="7">
+        <v>281</v>
+      </c>
+      <c t="s" r="J523" s="7">
+        <v>98</v>
+      </c>
       <c r="K523" s="7"/>
       <c r="L523" s="7"/>
       <c r="M523" s="7"/>
@@ -17500,7 +17506,7 @@
         <v>13</v>
       </c>
       <c r="B524" s="7">
-        <v>2831</v>
+        <v>2832</v>
       </c>
       <c t="s" r="C524" s="7">
         <v>136</v>
@@ -17513,65 +17519,65 @@
         <v>330</v>
       </c>
       <c t="s" r="G524" s="8">
+        <v>417</v>
+      </c>
+      <c t="s" r="H524" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H524" s="8">
-        <v>417</v>
-      </c>
       <c t="s" r="I524" s="7">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c t="s" r="J524" s="7">
-        <v>98</v>
+        <v>418</v>
       </c>
       <c r="K524" s="7"/>
       <c r="L524" s="7"/>
       <c r="M524" s="7"/>
     </row>
     <row r="525" ht="15" customHeight="1">
-      <c t="s" r="A525" s="6">
-        <v>13</v>
-      </c>
-      <c r="B525" s="7">
-        <v>2832</v>
-      </c>
-      <c t="s" r="C525" s="7">
-        <v>136</v>
-      </c>
+      <c r="A525" s="6"/>
+      <c r="B525" s="7"/>
+      <c r="C525" s="7"/>
       <c r="D525" s="7"/>
-      <c t="s" r="E525" s="7">
-        <v>416</v>
-      </c>
-      <c r="F525" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G525" s="8">
-        <v>417</v>
-      </c>
-      <c t="s" r="H525" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I525" s="7">
-        <v>267</v>
-      </c>
-      <c t="s" r="J525" s="7">
-        <v>418</v>
-      </c>
+      <c r="E525" s="7"/>
+      <c r="F525" s="7"/>
+      <c r="G525" s="8"/>
+      <c r="H525" s="8"/>
+      <c r="I525" s="7"/>
+      <c r="J525" s="7"/>
       <c r="K525" s="7"/>
       <c r="L525" s="7"/>
       <c r="M525" s="7"/>
     </row>
     <row r="526" ht="14.25" customHeight="1">
-      <c r="A526" s="6"/>
-      <c r="B526" s="7"/>
-      <c r="C526" s="7"/>
+      <c t="s" r="A526" s="6">
+        <v>13</v>
+      </c>
+      <c r="B526" s="7">
+        <v>1582</v>
+      </c>
+      <c t="s" r="C526" s="7">
+        <v>324</v>
+      </c>
       <c r="D526" s="7"/>
-      <c r="E526" s="7"/>
-      <c r="F526" s="7"/>
-      <c r="G526" s="8"/>
-      <c r="H526" s="8"/>
-      <c r="I526" s="7"/>
-      <c r="J526" s="7"/>
+      <c t="s" r="E526" s="7">
+        <v>419</v>
+      </c>
+      <c r="F526" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G526" s="8">
+        <v>97</v>
+      </c>
+      <c t="s" r="H526" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I526" s="7">
+        <v>28</v>
+      </c>
+      <c t="s" r="J526" s="7">
+        <v>239</v>
+      </c>
       <c r="K526" s="7"/>
       <c r="L526" s="7"/>
       <c r="M526" s="7"/>
@@ -17581,10 +17587,10 @@
         <v>13</v>
       </c>
       <c r="B527" s="7">
-        <v>1582</v>
+        <v>55</v>
       </c>
       <c t="s" r="C527" s="7">
-        <v>323</v>
+        <v>14</v>
       </c>
       <c r="D527" s="7"/>
       <c t="s" r="E527" s="7">
@@ -17594,16 +17600,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G527" s="8">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c t="s" r="H527" s="8">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c t="s" r="I527" s="7">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c t="s" r="J527" s="7">
-        <v>239</v>
+        <v>100</v>
       </c>
       <c r="K527" s="7"/>
       <c r="L527" s="7"/>
@@ -17614,7 +17620,7 @@
         <v>13</v>
       </c>
       <c r="B528" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="C528" s="7">
         <v>14</v>
@@ -17627,65 +17633,65 @@
         <v>330</v>
       </c>
       <c t="s" r="G528" s="8">
+        <v>420</v>
+      </c>
+      <c t="s" r="H528" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H528" s="8">
-        <v>420</v>
-      </c>
       <c t="s" r="I528" s="7">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c t="s" r="J528" s="7">
-        <v>100</v>
+        <v>221</v>
       </c>
       <c r="K528" s="7"/>
       <c r="L528" s="7"/>
       <c r="M528" s="7"/>
     </row>
     <row r="529" ht="14.25" customHeight="1">
-      <c t="s" r="A529" s="6">
-        <v>13</v>
-      </c>
-      <c r="B529" s="7">
-        <v>56</v>
-      </c>
-      <c t="s" r="C529" s="7">
-        <v>14</v>
-      </c>
+      <c r="A529" s="6"/>
+      <c r="B529" s="7"/>
+      <c r="C529" s="7"/>
       <c r="D529" s="7"/>
-      <c t="s" r="E529" s="7">
-        <v>419</v>
-      </c>
-      <c r="F529" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G529" s="8">
-        <v>420</v>
-      </c>
-      <c t="s" r="H529" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I529" s="7">
-        <v>39</v>
-      </c>
-      <c t="s" r="J529" s="7">
-        <v>221</v>
-      </c>
+      <c r="E529" s="7"/>
+      <c r="F529" s="7"/>
+      <c r="G529" s="8"/>
+      <c r="H529" s="8"/>
+      <c r="I529" s="7"/>
+      <c r="J529" s="7"/>
       <c r="K529" s="7"/>
       <c r="L529" s="7"/>
       <c r="M529" s="7"/>
     </row>
     <row r="530" ht="15" customHeight="1">
-      <c r="A530" s="6"/>
-      <c r="B530" s="7"/>
-      <c r="C530" s="7"/>
+      <c t="s" r="A530" s="6">
+        <v>13</v>
+      </c>
+      <c r="B530" s="7">
+        <v>83</v>
+      </c>
+      <c t="s" r="C530" s="7">
+        <v>14</v>
+      </c>
       <c r="D530" s="7"/>
-      <c r="E530" s="7"/>
-      <c r="F530" s="7"/>
-      <c r="G530" s="8"/>
-      <c r="H530" s="8"/>
-      <c r="I530" s="7"/>
-      <c r="J530" s="7"/>
+      <c t="s" r="E530" s="7">
+        <v>421</v>
+      </c>
+      <c r="F530" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G530" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H530" s="8">
+        <v>422</v>
+      </c>
+      <c t="s" r="I530" s="7">
+        <v>166</v>
+      </c>
+      <c t="s" r="J530" s="7">
+        <v>373</v>
+      </c>
       <c r="K530" s="7"/>
       <c r="L530" s="7"/>
       <c r="M530" s="7"/>
@@ -17695,7 +17701,7 @@
         <v>13</v>
       </c>
       <c r="B531" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="C531" s="7">
         <v>14</v>
@@ -17708,65 +17714,65 @@
         <v>330</v>
       </c>
       <c t="s" r="G531" s="8">
-        <v>23</v>
+        <v>422</v>
       </c>
       <c t="s" r="H531" s="8">
-        <v>422</v>
+        <v>23</v>
       </c>
       <c t="s" r="I531" s="7">
-        <v>166</v>
+        <v>423</v>
       </c>
       <c t="s" r="J531" s="7">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="K531" s="7"/>
       <c r="L531" s="7"/>
       <c r="M531" s="7"/>
     </row>
     <row r="532" ht="14.25" customHeight="1">
-      <c t="s" r="A532" s="6">
-        <v>13</v>
-      </c>
-      <c r="B532" s="7">
-        <v>84</v>
-      </c>
-      <c t="s" r="C532" s="7">
-        <v>14</v>
-      </c>
+      <c r="A532" s="6"/>
+      <c r="B532" s="7"/>
+      <c r="C532" s="7"/>
       <c r="D532" s="7"/>
-      <c t="s" r="E532" s="7">
-        <v>421</v>
-      </c>
-      <c r="F532" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G532" s="8">
-        <v>422</v>
-      </c>
-      <c t="s" r="H532" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="I532" s="7">
-        <v>423</v>
-      </c>
-      <c t="s" r="J532" s="7">
-        <v>334</v>
-      </c>
+      <c r="E532" s="7"/>
+      <c r="F532" s="7"/>
+      <c r="G532" s="8"/>
+      <c r="H532" s="8"/>
+      <c r="I532" s="7"/>
+      <c r="J532" s="7"/>
       <c r="K532" s="7"/>
       <c r="L532" s="7"/>
       <c r="M532" s="7"/>
     </row>
     <row r="533" ht="14.25" customHeight="1">
-      <c r="A533" s="6"/>
-      <c r="B533" s="7"/>
-      <c r="C533" s="7"/>
+      <c t="s" r="A533" s="6">
+        <v>13</v>
+      </c>
+      <c r="B533" s="7">
+        <v>629</v>
+      </c>
+      <c t="s" r="C533" s="7">
+        <v>14</v>
+      </c>
       <c r="D533" s="7"/>
-      <c r="E533" s="7"/>
-      <c r="F533" s="7"/>
-      <c r="G533" s="8"/>
-      <c r="H533" s="8"/>
-      <c r="I533" s="7"/>
-      <c r="J533" s="7"/>
+      <c t="s" r="E533" s="7">
+        <v>424</v>
+      </c>
+      <c r="F533" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G533" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H533" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="I533" s="7">
+        <v>201</v>
+      </c>
+      <c t="s" r="J533" s="7">
+        <v>312</v>
+      </c>
       <c r="K533" s="7"/>
       <c r="L533" s="7"/>
       <c r="M533" s="7"/>
@@ -17776,7 +17782,7 @@
         <v>13</v>
       </c>
       <c r="B534" s="7">
-        <v>629</v>
+        <v>85</v>
       </c>
       <c t="s" r="C534" s="7">
         <v>14</v>
@@ -17789,65 +17795,65 @@
         <v>330</v>
       </c>
       <c t="s" r="G534" s="8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c t="s" r="H534" s="8">
-        <v>23</v>
+        <v>425</v>
       </c>
       <c t="s" r="I534" s="7">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c t="s" r="J534" s="7">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="K534" s="7"/>
       <c r="L534" s="7"/>
       <c r="M534" s="7"/>
     </row>
     <row r="535" ht="15" customHeight="1">
-      <c t="s" r="A535" s="6">
-        <v>13</v>
-      </c>
-      <c r="B535" s="7">
-        <v>85</v>
-      </c>
-      <c t="s" r="C535" s="7">
-        <v>14</v>
-      </c>
+      <c r="A535" s="6"/>
+      <c r="B535" s="7"/>
+      <c r="C535" s="7"/>
       <c r="D535" s="7"/>
-      <c t="s" r="E535" s="7">
-        <v>424</v>
-      </c>
-      <c r="F535" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G535" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="H535" s="8">
-        <v>425</v>
-      </c>
-      <c t="s" r="I535" s="7">
-        <v>205</v>
-      </c>
-      <c t="s" r="J535" s="7">
-        <v>280</v>
-      </c>
+      <c r="E535" s="7"/>
+      <c r="F535" s="7"/>
+      <c r="G535" s="8"/>
+      <c r="H535" s="8"/>
+      <c r="I535" s="7"/>
+      <c r="J535" s="7"/>
       <c r="K535" s="7"/>
       <c r="L535" s="7"/>
       <c r="M535" s="7"/>
     </row>
     <row r="536" ht="14.25" customHeight="1">
-      <c r="A536" s="6"/>
-      <c r="B536" s="7"/>
-      <c r="C536" s="7"/>
+      <c t="s" r="A536" s="6">
+        <v>13</v>
+      </c>
+      <c r="B536" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="C536" s="7">
+        <v>14</v>
+      </c>
       <c r="D536" s="7"/>
-      <c r="E536" s="7"/>
-      <c r="F536" s="7"/>
-      <c r="G536" s="8"/>
-      <c r="H536" s="8"/>
-      <c r="I536" s="7"/>
-      <c r="J536" s="7"/>
+      <c t="s" r="E536" s="7">
+        <v>426</v>
+      </c>
+      <c r="F536" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G536" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H536" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I536" s="7">
+        <v>280</v>
+      </c>
+      <c t="s" r="J536" s="7">
+        <v>106</v>
+      </c>
       <c r="K536" s="7"/>
       <c r="L536" s="7"/>
       <c r="M536" s="7"/>
@@ -17857,7 +17863,7 @@
         <v>13</v>
       </c>
       <c r="B537" s="7">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c t="s" r="C537" s="7">
         <v>14</v>
@@ -17870,16 +17876,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G537" s="8">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c t="s" r="H537" s="8">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c t="s" r="I537" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J537" s="7">
-        <v>106</v>
+        <v>235</v>
       </c>
       <c r="K537" s="7"/>
       <c r="L537" s="7"/>
@@ -17890,7 +17896,7 @@
         <v>13</v>
       </c>
       <c r="B538" s="7">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c t="s" r="C538" s="7">
         <v>14</v>
@@ -17903,16 +17909,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G538" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H538" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H538" s="8">
-        <v>23</v>
-      </c>
       <c t="s" r="I538" s="7">
-        <v>281</v>
+        <v>62</v>
       </c>
       <c t="s" r="J538" s="7">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="K538" s="7"/>
       <c r="L538" s="7"/>
@@ -17923,7 +17929,7 @@
         <v>13</v>
       </c>
       <c r="B539" s="7">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c t="s" r="C539" s="7">
         <v>14</v>
@@ -17936,96 +17942,63 @@
         <v>330</v>
       </c>
       <c t="s" r="G539" s="8">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c t="s" r="H539" s="8">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c t="s" r="I539" s="7">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c t="s" r="J539" s="7">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="K539" s="7"/>
       <c r="L539" s="7"/>
       <c r="M539" s="7"/>
     </row>
-    <row r="540" ht="15" customHeight="1">
-      <c t="s" r="A540" s="6">
-        <v>13</v>
-      </c>
-      <c r="B540" s="7">
-        <v>193</v>
-      </c>
-      <c t="s" r="C540" s="7">
-        <v>14</v>
-      </c>
-      <c r="D540" s="7"/>
-      <c t="s" r="E540" s="7">
-        <v>426</v>
-      </c>
-      <c r="F540" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G540" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H540" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="I540" s="7">
-        <v>20</v>
-      </c>
-      <c t="s" r="J540" s="7">
-        <v>294</v>
-      </c>
-      <c r="K540" s="7"/>
-      <c r="L540" s="7"/>
-      <c r="M540" s="7"/>
-    </row>
-    <row r="541" ht="15.75" customHeight="1">
-      <c t="s" r="A541" s="9">
+    <row r="540" ht="16.5" customHeight="1">
+      <c t="s" r="A540" s="9">
         <v>427</v>
       </c>
-      <c r="B541" s="9"/>
-      <c r="C541" s="9"/>
-      <c r="D541" s="9"/>
-      <c r="E541" s="9"/>
-      <c r="F541" s="9"/>
-      <c r="G541" s="9"/>
-      <c r="H541" s="9"/>
-      <c r="I541" s="9"/>
-      <c r="J541" s="9"/>
-      <c r="K541" s="9"/>
-      <c r="L541" s="9"/>
-      <c r="M541" s="9"/>
-      <c r="N541" s="9"/>
-      <c r="O541" s="9"/>
-    </row>
-    <row r="542" ht="65.25" customHeight="1"/>
-    <row r="543" ht="16.5" customHeight="1">
-      <c t="s" r="A543" s="10">
+      <c r="B540" s="9"/>
+      <c r="C540" s="9"/>
+      <c r="D540" s="9"/>
+      <c r="E540" s="9"/>
+      <c r="F540" s="9"/>
+      <c r="G540" s="9"/>
+      <c r="H540" s="9"/>
+      <c r="I540" s="9"/>
+      <c r="J540" s="9"/>
+      <c r="K540" s="9"/>
+      <c r="L540" s="9"/>
+      <c r="M540" s="9"/>
+      <c r="N540" s="9"/>
+      <c r="O540" s="9"/>
+    </row>
+    <row r="541" ht="65.25" customHeight="1"/>
+    <row r="542" ht="16.5" customHeight="1">
+      <c t="s" r="A542" s="10">
         <v>428</v>
       </c>
-      <c r="B543" s="10"/>
-      <c r="C543" s="10"/>
-      <c r="D543" s="10"/>
-      <c r="E543" s="10"/>
-      <c r="F543" s="10"/>
-      <c r="G543" s="10"/>
-      <c r="H543" s="10"/>
-      <c r="I543" s="10"/>
-      <c r="J543" s="10"/>
-      <c r="K543" s="10"/>
-      <c t="s" r="L543" s="11">
+      <c r="B542" s="10"/>
+      <c r="C542" s="10"/>
+      <c r="D542" s="10"/>
+      <c r="E542" s="10"/>
+      <c r="F542" s="10"/>
+      <c r="G542" s="10"/>
+      <c r="H542" s="10"/>
+      <c r="I542" s="10"/>
+      <c r="J542" s="10"/>
+      <c r="K542" s="10"/>
+      <c t="s" r="L542" s="11">
         <v>429</v>
       </c>
-      <c r="M543" s="11"/>
-      <c r="N543" s="11"/>
+      <c r="M542" s="11"/>
+      <c r="N542" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="1076">
+  <mergeCells count="1074">
     <mergeCell ref="D1:O1"/>
     <mergeCell ref="D2:O2"/>
     <mergeCell ref="D3:O4"/>
@@ -19097,11 +19070,9 @@
     <mergeCell ref="K538:L538"/>
     <mergeCell ref="C539:D539"/>
     <mergeCell ref="K539:L539"/>
-    <mergeCell ref="C540:D540"/>
-    <mergeCell ref="K540:L540"/>
-    <mergeCell ref="A541:O541"/>
-    <mergeCell ref="A543:K543"/>
-    <mergeCell ref="L543:N543"/>
+    <mergeCell ref="A540:O540"/>
+    <mergeCell ref="A542:K542"/>
+    <mergeCell ref="L542:N542"/>
   </mergeCells>
   <pageMargins left="0.196666672825813" right="0.219999998807907" top="0.280000001192093" bottom="0.230000004172325" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
